--- a/SuppXLS/Scen_B_SYS_Additional_Assumptions.xlsx
+++ b/SuppXLS/Scen_B_SYS_Additional_Assumptions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\TIM-LEAF 050626\TIM-LEAF 050626\tim-leaf 050626\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91AF77D-2E8D-44EF-B8A8-7C6724294118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735F0215-4809-4FEC-9EA4-6CDE14667B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="29" r:id="rId1"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="266">
   <si>
     <t>UC_N</t>
   </si>
@@ -1052,7 +1052,7 @@
     <numFmt numFmtId="190" formatCode="0.0%"/>
     <numFmt numFmtId="191" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="136">
+  <fonts count="137">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1174,6 +1174,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2868,7 +2875,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -2880,133 +2887,133 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="4" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3016,70 +3023,70 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="121" fillId="44" borderId="0">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="122" fillId="44" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3091,32 +3098,32 @@
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3128,31 +3135,31 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3164,31 +3171,31 @@
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3200,46 +3207,46 @@
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3251,38 +3258,38 @@
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="84" fillId="54" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="85" fillId="54" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3294,47 +3301,47 @@
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3346,31 +3353,31 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3382,48 +3389,48 @@
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3435,699 +3442,699 @@
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="122" fillId="54" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="52" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="68" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="68" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="90" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="53" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="90" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="90" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="105" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="90" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="86" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="58" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="70" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="86" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="68" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="66" fillId="57" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="87" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="70" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="87" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="67" fillId="69" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="172" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="94" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="60" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="54" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="108" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="97" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="58" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="97" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4144,51 +4151,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="175" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="187" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4229,7 +4236,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4237,548 +4244,548 @@
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="2" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="93" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="94" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="97" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="69" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="98" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="97" fillId="0" borderId="0">
+    <xf numFmtId="173" fontId="98" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="98" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="99" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="99" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="65" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="50" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="190" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="120" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="121" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="191" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4788,90 +4795,90 @@
     <xf numFmtId="183" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="188" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="188" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="185" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="124" fillId="44" borderId="2">
+    <xf numFmtId="185" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="125" fillId="44" borderId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="83" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="125" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="109" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="83" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="126" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -4892,7 +4899,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4907,43 +4914,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="78" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="126" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="127" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4979,15 +4986,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -5030,10 +5037,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5051,9 +5058,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5077,13 +5084,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -5106,10 +5113,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -5117,28 +5124,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5146,7 +5153,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -5156,11 +5163,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5170,30 +5177,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="133" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="134" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
@@ -5237,7 +5244,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5329,146 +5336,146 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5476,9 +5483,9 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5486,16 +5493,16 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -5531,328 +5538,328 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="99" fillId="73" borderId="32">
+    <xf numFmtId="0" fontId="20" fillId="53" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="100" fillId="73" borderId="32">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="33">
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="33">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="92" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="93" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5865,112 +5872,112 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="13" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5991,90 +5998,90 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6095,7 +6102,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6106,34 +6113,34 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6144,189 +6151,189 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="119" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6335,671 +6342,671 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="116" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="100" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="55" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="100" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="101" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="68" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="101" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="57" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="123" fillId="74" borderId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="3" fontId="122" fillId="74" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="121" fillId="74" borderId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="127" fillId="74" borderId="0">
+    <xf numFmtId="3" fontId="128" fillId="74" borderId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="3" fontId="124" fillId="9" borderId="2">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="3" fontId="125" fillId="9" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="131" fillId="74" borderId="0">
+    <xf numFmtId="3" fontId="132" fillId="74" borderId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -7062,8 +7069,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -7086,7 +7093,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -7180,173 +7187,173 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="86" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="117" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="118" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -7365,7 +7372,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -7374,71 +7381,71 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -7450,7 +7457,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="120" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="121" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -7464,7 +7471,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7549,6 +7556,7 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7573,45 +7581,45 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="14" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="45" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="17" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="21" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="16" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="17" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="18" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="19" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="16" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -13320,12 +13328,12 @@
       <c r="Z15" s="22"/>
     </row>
     <row r="16" spans="1:26" ht="102.75" customHeight="1">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="89" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="24"/>
@@ -13409,11 +13417,11 @@
       <c r="A19" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
       <c r="G19" s="30"/>
@@ -13441,11 +13449,11 @@
       <c r="A20" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="88" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="29"/>
       <c r="F20" s="29"/>
       <c r="G20" s="30"/>
@@ -13533,11 +13541,11 @@
       <c r="A23" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="87" t="s">
+      <c r="B23" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="87"/>
-      <c r="D23" s="87"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -13623,11 +13631,11 @@
       <c r="A26" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="87" t="s">
+      <c r="B26" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -13743,11 +13751,11 @@
       <c r="A30" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="89" t="s">
+      <c r="B30" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="C30" s="87"/>
-      <c r="D30" s="87"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
       <c r="G30" s="22"/>
@@ -13775,11 +13783,11 @@
       <c r="A31" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="87"/>
-      <c r="D31" s="87"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
       <c r="E31" s="33"/>
       <c r="F31" s="33"/>
       <c r="G31" s="22"/>
@@ -16983,28 +16991,25 @@
     </row>
     <row r="27" spans="2:12">
       <c r="B27" s="39" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>107</v>
+        <v>89</v>
+      </c>
+      <c r="E27" s="41">
+        <v>2026</v>
+      </c>
+      <c r="F27" s="39">
+        <v>0</v>
+      </c>
+      <c r="G27" s="39">
+        <v>0</v>
       </c>
       <c r="I27" s="39" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="L27" s="40" t="s">
         <v>175</v>
@@ -17483,27 +17488,27 @@
       </c>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="43" t="s">
+      <c r="B55" s="44" t="s">
         <v>160</v>
       </c>
       <c r="C55" s="18"/>
-      <c r="D55" s="80" t="s">
+      <c r="D55" s="81" t="s">
         <v>161</v>
       </c>
       <c r="E55" s="18"/>
-      <c r="F55" s="43">
+      <c r="F55" s="44">
         <v>2032</v>
       </c>
-      <c r="G55" s="83" t="s">
+      <c r="G55" s="84" t="s">
         <v>81</v>
       </c>
       <c r="H55" s="18">
         <v>1</v>
       </c>
-      <c r="I55" s="83">
+      <c r="I55" s="84">
         <v>10</v>
       </c>
-      <c r="J55" s="43" t="s">
+      <c r="J55" s="44" t="s">
         <v>167</v>
       </c>
     </row>
@@ -17591,7 +17596,7 @@
       <c r="B62" t="s">
         <v>166</v>
       </c>
-      <c r="J62" s="84" t="s">
+      <c r="J62" s="85" t="s">
         <v>248</v>
       </c>
     </row>
@@ -17786,8 +17791,8 @@
     <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" customWidth="1"/>
+    <col min="9" max="9" width="40.26953125" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="30.26953125" customWidth="1"/>
     <col min="12" max="12" width="44.7265625" bestFit="1" customWidth="1"/>
@@ -17884,7 +17889,7 @@
         <v>111</v>
       </c>
       <c r="C6" s="39"/>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="42" t="s">
         <v>190</v>
       </c>
       <c r="E6" s="39"/>
@@ -17929,7 +17934,7 @@
     <row r="7" spans="1:22">
       <c r="B7" s="38"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="41"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
       <c r="G7" s="38">
@@ -17960,7 +17965,7 @@
         <v>115</v>
       </c>
       <c r="C8" s="39"/>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="42" t="s">
         <v>113</v>
       </c>
       <c r="E8" s="38"/>
@@ -18006,7 +18011,7 @@
     <row r="9" spans="1:22">
       <c r="B9" s="38"/>
       <c r="C9" s="39"/>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="42" t="s">
         <v>113</v>
       </c>
       <c r="E9" s="38"/>
@@ -18037,7 +18042,7 @@
     <row r="10" spans="1:22">
       <c r="B10" s="38"/>
       <c r="C10" s="38"/>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="42" t="s">
         <v>113</v>
       </c>
       <c r="E10" s="38"/>
@@ -18077,7 +18082,7 @@
     <row r="11" spans="1:22">
       <c r="B11" s="38"/>
       <c r="C11" s="38"/>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="42" t="s">
         <v>113</v>
       </c>
       <c r="E11" s="38"/>
@@ -18117,7 +18122,7 @@
     <row r="12" spans="1:22">
       <c r="B12" s="38"/>
       <c r="C12" s="38"/>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="42" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="38"/>
@@ -18157,7 +18162,7 @@
     <row r="13" spans="1:22">
       <c r="B13" s="38"/>
       <c r="C13" s="38"/>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="42" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="38"/>
@@ -18194,7 +18199,7 @@
     <row r="14" spans="1:22">
       <c r="B14" s="38"/>
       <c r="C14" s="38"/>
-      <c r="D14" s="41"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="38"/>
       <c r="F14" s="39"/>
       <c r="G14" s="39"/>
@@ -18653,42 +18658,42 @@
       <c r="B54" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="C54" s="51" t="s">
+      <c r="C54" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="51" t="s">
+      <c r="D54" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="52">
         <v>2020</v>
       </c>
-      <c r="F54" s="51">
+      <c r="F54" s="52">
         <v>2025</v>
       </c>
-      <c r="G54" s="51">
+      <c r="G54" s="52">
         <v>2030</v>
       </c>
-      <c r="H54" s="51">
+      <c r="H54" s="52">
         <v>2035</v>
       </c>
-      <c r="I54" s="51">
+      <c r="I54" s="52">
         <v>2040</v>
       </c>
-      <c r="J54" s="51">
+      <c r="J54" s="52">
         <v>2045</v>
       </c>
-      <c r="K54" s="51">
+      <c r="K54" s="52">
         <v>2050</v>
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="44" t="s">
+      <c r="B55" s="45" t="s">
         <v>183</v>
       </c>
       <c r="C55" s="19">
         <v>34.700000000000003</v>
       </c>
-      <c r="D55" s="47">
+      <c r="D55" s="48">
         <v>9.6388888888888893</v>
       </c>
       <c r="E55" s="19">
@@ -18714,13 +18719,13 @@
       </c>
     </row>
     <row r="56" spans="2:11">
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="43" t="s">
         <v>184</v>
       </c>
       <c r="C56" s="19">
         <v>34.700000000000003</v>
       </c>
-      <c r="D56" s="47">
+      <c r="D56" s="48">
         <v>9.6388888888888893</v>
       </c>
       <c r="E56" s="19">
@@ -18746,13 +18751,13 @@
       </c>
     </row>
     <row r="57" spans="2:11">
-      <c r="B57" s="42" t="s">
+      <c r="B57" s="43" t="s">
         <v>185</v>
       </c>
       <c r="C57" s="19">
         <v>36.6</v>
       </c>
-      <c r="D57" s="47">
+      <c r="D57" s="48">
         <v>10.166666666666666</v>
       </c>
       <c r="E57" s="19">
@@ -18778,69 +18783,69 @@
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="45" t="s">
+      <c r="B58" s="46" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="43">
+      <c r="C58" s="44">
         <v>40.299999999999997</v>
       </c>
-      <c r="D58" s="48">
+      <c r="D58" s="49">
         <v>11.194444444444443</v>
       </c>
-      <c r="E58" s="43">
+      <c r="E58" s="44">
         <v>0</v>
       </c>
-      <c r="F58" s="43">
+      <c r="F58" s="44">
         <v>0</v>
       </c>
-      <c r="G58" s="43">
+      <c r="G58" s="44">
         <v>0</v>
       </c>
-      <c r="H58" s="43">
+      <c r="H58" s="44">
         <v>3.6</v>
       </c>
-      <c r="I58" s="43">
+      <c r="I58" s="44">
         <v>36</v>
       </c>
-      <c r="J58" s="43">
+      <c r="J58" s="44">
         <v>36</v>
       </c>
-      <c r="K58" s="43">
+      <c r="K58" s="44">
         <v>36</v>
       </c>
     </row>
     <row r="59" spans="2:11">
-      <c r="C59" s="46"/>
-      <c r="D59" s="46" t="s">
+      <c r="C59" s="47"/>
+      <c r="D59" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="E59" s="46">
+      <c r="E59" s="47">
         <v>1.8</v>
       </c>
-      <c r="F59" s="46">
+      <c r="F59" s="47">
         <v>5.4</v>
       </c>
-      <c r="G59" s="46">
+      <c r="G59" s="47">
         <v>73.8</v>
       </c>
-      <c r="H59" s="46">
+      <c r="H59" s="47">
         <v>95.399999999999991</v>
       </c>
-      <c r="I59" s="46">
+      <c r="I59" s="47">
         <v>147.6</v>
       </c>
-      <c r="J59" s="46">
+      <c r="J59" s="47">
         <v>158.4</v>
       </c>
-      <c r="K59" s="46">
+      <c r="K59" s="47">
         <v>158.4</v>
       </c>
     </row>
     <row r="60" spans="2:11">
-      <c r="B60" s="49" t="s">
+      <c r="B60" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="C60" s="51" t="s">
         <v>189</v>
       </c>
     </row>
@@ -19131,10 +19136,10 @@
       <c r="D5" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="85" t="s">
+      <c r="H5" s="86" t="s">
         <v>250</v>
       </c>
-      <c r="I5" s="85" t="str">
+      <c r="I5" s="86" t="str">
         <f>H5</f>
         <v>*0.85</v>
       </c>
@@ -19143,20 +19148,20 @@
       </c>
     </row>
     <row r="6" spans="2:13">
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="86"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-    </row>
-    <row r="9" spans="2:13" s="52" customFormat="1"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+    </row>
+    <row r="9" spans="2:13" s="53" customFormat="1"/>
     <row r="11" spans="2:13">
-      <c r="B11" s="73" t="str">
+      <c r="B11" s="74" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C11" s="73"/>
+      <c r="C11" s="74"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="4" t="s">
@@ -19169,34 +19174,34 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="77" t="s">
         <v>253</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="G14" s="77" t="s">
         <v>9</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I14" s="77" t="s">
+      <c r="I14" s="78" t="s">
         <v>251</v>
       </c>
-      <c r="J14" s="77" t="s">
+      <c r="J14" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="K14" s="75" t="s">
+      <c r="K14" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -19228,11 +19233,11 @@
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15" s="74">
+      <c r="I15" s="75">
         <f>MIN(C62:H62)/1000</f>
         <v>84.308999999999997</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="75">
         <v>5</v>
       </c>
       <c r="K15" s="19" t="s">
@@ -19262,11 +19267,11 @@
       <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16" s="74">
+      <c r="I16" s="75">
         <f>I15*1.1</f>
         <v>92.739900000000006</v>
       </c>
-      <c r="J16" s="74"/>
+      <c r="J16" s="75"/>
       <c r="K16" s="19"/>
     </row>
     <row r="17" spans="2:13">
@@ -19286,10 +19291,10 @@
       <c r="H17">
         <v>1</v>
       </c>
-      <c r="I17" s="74">
+      <c r="I17" s="75">
         <v>0</v>
       </c>
-      <c r="J17" s="74"/>
+      <c r="J17" s="75"/>
       <c r="K17" s="19"/>
     </row>
     <row r="18" spans="2:13">
@@ -19314,11 +19319,11 @@
       <c r="H18">
         <v>1</v>
       </c>
-      <c r="I18" s="74">
+      <c r="I18" s="75">
         <f>1.2*MAX(C74:H74)/1000</f>
         <v>266.64</v>
       </c>
-      <c r="J18" s="74">
+      <c r="J18" s="75">
         <v>5</v>
       </c>
       <c r="K18" s="19" t="s">
@@ -19348,37 +19353,37 @@
       <c r="H19">
         <v>1</v>
       </c>
-      <c r="I19" s="74">
+      <c r="I19" s="75">
         <f>+I18*1.3</f>
         <v>346.63200000000001</v>
       </c>
-      <c r="J19" s="74"/>
+      <c r="J19" s="75"/>
       <c r="K19" s="19"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="43"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="18"/>
-      <c r="D20" s="80" t="s">
+      <c r="D20" s="81" t="s">
         <v>196</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="44">
         <v>2050</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H20" s="18">
         <v>1</v>
       </c>
-      <c r="I20" s="78">
+      <c r="I20" s="79">
         <f>I18*5</f>
         <v>1333.1999999999998</v>
       </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="43"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="44"/>
       <c r="M20" s="18"/>
     </row>
     <row r="21" spans="2:13">
@@ -19393,11 +19398,11 @@
       <c r="G22" s="19"/>
     </row>
     <row r="23" spans="2:13">
-      <c r="B23" s="73" t="str">
+      <c r="B23" s="74" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C23" s="73"/>
+      <c r="C23" s="74"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="4" t="s">
@@ -19410,34 +19415,34 @@
       </c>
     </row>
     <row r="26" spans="2:13">
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="77" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E26" s="76" t="s">
+      <c r="E26" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="76" t="s">
+      <c r="G26" s="77" t="s">
         <v>9</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I26" s="77" t="s">
+      <c r="I26" s="78" t="s">
         <v>251</v>
       </c>
-      <c r="J26" s="77" t="s">
+      <c r="J26" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="K26" s="75" t="s">
+      <c r="K26" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L26" s="5" t="s">
@@ -19469,7 +19474,7 @@
       <c r="H27">
         <v>1</v>
       </c>
-      <c r="I27" s="81">
+      <c r="I27" s="82">
         <f>MIN(C78:H78)*0.5/1000</f>
         <v>1.0561541074426846</v>
       </c>
@@ -19503,7 +19508,7 @@
       <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" s="81">
+      <c r="I28" s="82">
         <v>0</v>
       </c>
       <c r="K28" s="19"/>
@@ -19525,7 +19530,7 @@
       <c r="H29">
         <v>1</v>
       </c>
-      <c r="I29" s="81">
+      <c r="I29" s="82">
         <v>0</v>
       </c>
       <c r="K29" s="19"/>
@@ -19552,7 +19557,7 @@
       <c r="H30">
         <v>1</v>
       </c>
-      <c r="I30" s="81">
+      <c r="I30" s="82">
         <f>2*MAX(C78:H78)/1000</f>
         <v>5.370076461803917</v>
       </c>
@@ -19570,47 +19575,47 @@
       </c>
     </row>
     <row r="31" spans="2:13">
-      <c r="B31" s="43"/>
+      <c r="B31" s="44"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="80" t="s">
+      <c r="D31" s="81" t="s">
         <v>201</v>
       </c>
       <c r="E31" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F31" s="43">
+      <c r="F31" s="44">
         <v>2040</v>
       </c>
-      <c r="G31" s="43" t="s">
+      <c r="G31" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H31" s="18">
         <v>1</v>
       </c>
-      <c r="I31" s="79">
+      <c r="I31" s="80">
         <f>I30*2</f>
         <v>10.740152923607834</v>
       </c>
       <c r="J31" s="18"/>
-      <c r="K31" s="43"/>
+      <c r="K31" s="44"/>
     </row>
     <row r="32" spans="2:13">
-      <c r="D32" s="80" t="s">
+      <c r="D32" s="81" t="s">
         <v>201</v>
       </c>
       <c r="E32" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="43">
+      <c r="F32" s="44">
         <v>2050</v>
       </c>
-      <c r="G32" s="43" t="s">
+      <c r="G32" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H32" s="18">
         <v>1</v>
       </c>
-      <c r="I32" s="79">
+      <c r="I32" s="80">
         <f>I31*5</f>
         <v>53.700764618039173</v>
       </c>
@@ -19625,11 +19630,11 @@
       <c r="G34" s="19"/>
     </row>
     <row r="35" spans="2:13">
-      <c r="B35" s="73" t="str">
+      <c r="B35" s="74" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C35" s="73"/>
+      <c r="C35" s="74"/>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="4" t="s">
@@ -19642,34 +19647,34 @@
       </c>
     </row>
     <row r="38" spans="2:13">
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="77" t="s">
         <v>253</v>
       </c>
-      <c r="D38" s="76" t="s">
+      <c r="D38" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E38" s="76" t="s">
+      <c r="E38" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="F38" s="76" t="s">
+      <c r="F38" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="76" t="s">
+      <c r="G38" s="77" t="s">
         <v>9</v>
       </c>
       <c r="H38" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I38" s="77" t="s">
+      <c r="I38" s="78" t="s">
         <v>251</v>
       </c>
-      <c r="J38" s="77" t="s">
+      <c r="J38" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="K38" s="75" t="s">
+      <c r="K38" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L38" s="5" t="s">
@@ -19701,7 +19706,7 @@
       <c r="H39">
         <v>1</v>
       </c>
-      <c r="I39" s="81">
+      <c r="I39" s="82">
         <f>MIN(C77:H77)*0.5/1000</f>
         <v>0.45905338863054296</v>
       </c>
@@ -19735,7 +19740,7 @@
       <c r="H40">
         <v>1</v>
       </c>
-      <c r="I40" s="81">
+      <c r="I40" s="82">
         <v>0</v>
       </c>
       <c r="J40" s="19"/>
@@ -19758,7 +19763,7 @@
       <c r="H41">
         <v>1</v>
       </c>
-      <c r="I41" s="81">
+      <c r="I41" s="82">
         <v>0</v>
       </c>
       <c r="J41" s="19"/>
@@ -19786,7 +19791,7 @@
       <c r="H42">
         <v>1</v>
       </c>
-      <c r="I42" s="81">
+      <c r="I42" s="82">
         <f>2*MAX(C77:H77)/1000</f>
         <v>2.3340834255383354</v>
       </c>
@@ -19804,47 +19809,47 @@
       </c>
     </row>
     <row r="43" spans="2:13">
-      <c r="B43" s="43"/>
+      <c r="B43" s="44"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="80" t="s">
+      <c r="D43" s="81" t="s">
         <v>200</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F43" s="43">
+      <c r="F43" s="44">
         <v>2040</v>
       </c>
-      <c r="G43" s="43" t="s">
+      <c r="G43" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H43" s="18">
         <v>1</v>
       </c>
-      <c r="I43" s="79">
+      <c r="I43" s="80">
         <f>I42*2</f>
         <v>4.6681668510766707</v>
       </c>
-      <c r="J43" s="43"/>
-      <c r="K43" s="43"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="44"/>
     </row>
     <row r="44" spans="2:13">
-      <c r="D44" s="80" t="s">
+      <c r="D44" s="81" t="s">
         <v>200</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F44" s="43">
+      <c r="F44" s="44">
         <v>2050</v>
       </c>
-      <c r="G44" s="43" t="s">
+      <c r="G44" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H44" s="18">
         <v>1</v>
       </c>
-      <c r="I44" s="79">
+      <c r="I44" s="80">
         <f>I43*5</f>
         <v>23.340834255383353</v>
       </c>
@@ -19853,62 +19858,62 @@
     <row r="45" spans="2:13">
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
-      <c r="I45" s="82"/>
+      <c r="I45" s="83"/>
     </row>
     <row r="46" spans="2:13">
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
-      <c r="I46" s="82"/>
+      <c r="I46" s="83"/>
     </row>
     <row r="47" spans="2:13">
-      <c r="B47" s="73" t="str">
+      <c r="B47" s="74" t="str">
         <f>"~UC_Sets: R_E: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3:D3)</f>
         <v>~UC_Sets: R_E: IE,National</v>
       </c>
-      <c r="C47" s="73"/>
-      <c r="I47" s="82"/>
+      <c r="C47" s="74"/>
+      <c r="I47" s="83"/>
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I48" s="82"/>
+      <c r="I48" s="83"/>
     </row>
     <row r="49" spans="2:13">
       <c r="G49" t="s">
         <v>7</v>
       </c>
-      <c r="I49" s="82"/>
+      <c r="I49" s="83"/>
     </row>
     <row r="50" spans="2:13">
-      <c r="B50" s="75" t="s">
+      <c r="B50" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="76" t="s">
+      <c r="C50" s="77" t="s">
         <v>253</v>
       </c>
-      <c r="D50" s="76" t="s">
+      <c r="D50" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E50" s="76" t="s">
+      <c r="E50" s="77" t="s">
         <v>197</v>
       </c>
-      <c r="F50" s="76" t="s">
+      <c r="F50" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="G50" s="76" t="s">
+      <c r="G50" s="77" t="s">
         <v>9</v>
       </c>
       <c r="H50" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="I50" s="77" t="s">
+      <c r="I50" s="78" t="s">
         <v>251</v>
       </c>
-      <c r="J50" s="77" t="s">
+      <c r="J50" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="K50" s="75" t="s">
+      <c r="K50" s="76" t="s">
         <v>11</v>
       </c>
       <c r="L50" s="5" t="s">
@@ -19940,7 +19945,7 @@
       <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51" s="81">
+      <c r="I51" s="82">
         <f>MIN(C76:H76)*0.5/1000</f>
         <v>14.343833406839419</v>
       </c>
@@ -19974,7 +19979,7 @@
       <c r="H52">
         <v>1</v>
       </c>
-      <c r="I52" s="81">
+      <c r="I52" s="82">
         <v>0</v>
       </c>
       <c r="J52" s="19"/>
@@ -19999,7 +20004,7 @@
       <c r="H53">
         <v>1</v>
       </c>
-      <c r="I53" s="81">
+      <c r="I53" s="82">
         <v>0</v>
       </c>
       <c r="J53" s="19"/>
@@ -20027,7 +20032,7 @@
       <c r="H54">
         <v>1</v>
       </c>
-      <c r="I54" s="81">
+      <c r="I54" s="82">
         <f>2*MAX(C76:H76)/1000</f>
         <v>72.932048085875735</v>
       </c>
@@ -20045,49 +20050,49 @@
       </c>
     </row>
     <row r="55" spans="2:13">
-      <c r="B55" s="43"/>
+      <c r="B55" s="44"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="80" t="s">
+      <c r="D55" s="81" t="s">
         <v>199</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F55" s="43">
+      <c r="F55" s="44">
         <v>2040</v>
       </c>
-      <c r="G55" s="43" t="s">
+      <c r="G55" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H55" s="18">
         <v>1</v>
       </c>
-      <c r="I55" s="79">
+      <c r="I55" s="80">
         <f>I54*2</f>
         <v>145.86409617175147</v>
       </c>
-      <c r="J55" s="43"/>
-      <c r="K55" s="43" t="s">
+      <c r="J55" s="44"/>
+      <c r="K55" s="44" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="56" spans="2:13">
-      <c r="D56" s="80" t="s">
+      <c r="D56" s="81" t="s">
         <v>199</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="F56" s="43">
+      <c r="F56" s="44">
         <v>2050</v>
       </c>
-      <c r="G56" s="43" t="s">
+      <c r="G56" s="44" t="s">
         <v>81</v>
       </c>
       <c r="H56" s="18">
         <v>1</v>
       </c>
-      <c r="I56" s="79">
+      <c r="I56" s="80">
         <f>I55*5</f>
         <v>729.32048085875738</v>
       </c>
@@ -20098,247 +20103,247 @@
       <c r="G57" s="19"/>
     </row>
     <row r="60" spans="2:13">
-      <c r="B60" s="57" t="s">
+      <c r="B60" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="C60" s="57"/>
-      <c r="D60" s="57"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
     </row>
     <row r="61" spans="2:13" ht="15.5">
-      <c r="B61" s="57"/>
-      <c r="C61" s="63">
+      <c r="B61" s="58"/>
+      <c r="C61" s="64">
         <v>2018</v>
       </c>
-      <c r="D61" s="63">
+      <c r="D61" s="64">
         <v>2019</v>
       </c>
-      <c r="E61" s="63">
+      <c r="E61" s="64">
         <v>2020</v>
       </c>
-      <c r="F61" s="63">
+      <c r="F61" s="64">
         <v>2021</v>
       </c>
-      <c r="G61" s="63">
+      <c r="G61" s="64">
         <v>2022</v>
       </c>
-      <c r="H61" s="63">
+      <c r="H61" s="64">
         <v>2023</v>
       </c>
     </row>
     <row r="62" spans="2:13">
-      <c r="B62" s="58" t="s">
+      <c r="B62" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="C62" s="59">
+      <c r="C62" s="60">
         <v>121157</v>
       </c>
-      <c r="D62" s="59">
+      <c r="D62" s="60">
         <v>113305</v>
       </c>
-      <c r="E62" s="59">
+      <c r="E62" s="60">
         <v>84309</v>
       </c>
-      <c r="F62" s="59">
+      <c r="F62" s="60">
         <v>101853</v>
       </c>
-      <c r="G62" s="59">
+      <c r="G62" s="60">
         <v>101349</v>
       </c>
-      <c r="H62" s="59">
+      <c r="H62" s="60">
         <v>117424</v>
       </c>
     </row>
     <row r="63" spans="2:13">
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="59">
+      <c r="C63" s="60">
         <v>25459</v>
       </c>
-      <c r="D63" s="59">
+      <c r="D63" s="60">
         <v>24645</v>
       </c>
-      <c r="E63" s="59">
+      <c r="E63" s="60">
         <v>21495</v>
       </c>
-      <c r="F63" s="59">
+      <c r="F63" s="60">
         <v>28387</v>
       </c>
-      <c r="G63" s="59">
+      <c r="G63" s="60">
         <v>23655</v>
       </c>
-      <c r="H63" s="59">
+      <c r="H63" s="60">
         <v>29038</v>
       </c>
     </row>
     <row r="64" spans="2:13">
-      <c r="B64" s="58" t="s">
+      <c r="B64" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="C64" s="59">
+      <c r="C64" s="60">
         <v>157865</v>
       </c>
-      <c r="D64" s="59">
+      <c r="D64" s="60">
         <v>149748</v>
       </c>
-      <c r="E64" s="59">
+      <c r="E64" s="60">
         <v>10710</v>
       </c>
-      <c r="F64" s="59">
+      <c r="F64" s="60">
         <v>12136</v>
       </c>
-      <c r="G64" s="59">
+      <c r="G64" s="60">
         <v>12244</v>
       </c>
-      <c r="H64" s="59">
+      <c r="H64" s="60">
         <v>13316</v>
       </c>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="58" t="s">
+      <c r="B65" s="59" t="s">
         <v>206</v>
       </c>
-      <c r="C65" s="62">
+      <c r="C65" s="63">
         <v>304481</v>
       </c>
-      <c r="D65" s="62">
+      <c r="D65" s="63">
         <v>287698</v>
       </c>
-      <c r="E65" s="62">
+      <c r="E65" s="63">
         <v>116514</v>
       </c>
-      <c r="F65" s="62">
+      <c r="F65" s="63">
         <v>142376</v>
       </c>
-      <c r="G65" s="62">
+      <c r="G65" s="63">
         <v>137248</v>
       </c>
-      <c r="H65" s="62">
+      <c r="H65" s="63">
         <v>159778</v>
       </c>
     </row>
     <row r="66" spans="2:8">
-      <c r="B66" s="58" t="s">
+      <c r="B66" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="C66" s="59">
+      <c r="C66" s="60">
         <v>99456</v>
       </c>
-      <c r="D66" s="59">
+      <c r="D66" s="60">
         <v>108895</v>
       </c>
-      <c r="E66" s="59">
+      <c r="E66" s="60">
         <v>78541</v>
       </c>
-      <c r="F66" s="59">
+      <c r="F66" s="60">
         <v>68042</v>
       </c>
-      <c r="G66" s="59">
+      <c r="G66" s="60">
         <v>46567</v>
       </c>
-      <c r="H66" s="59">
+      <c r="H66" s="60">
         <v>50381</v>
       </c>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="58" t="s">
+      <c r="B67" s="59" t="s">
         <v>208</v>
       </c>
-      <c r="C67" s="59">
+      <c r="C67" s="60">
         <v>14859</v>
       </c>
-      <c r="D67" s="59">
+      <c r="D67" s="60">
         <v>15152</v>
       </c>
-      <c r="E67" s="59">
+      <c r="E67" s="60">
         <v>11573</v>
       </c>
-      <c r="F67" s="59">
+      <c r="F67" s="60">
         <v>10631</v>
       </c>
-      <c r="G67" s="59">
+      <c r="G67" s="60">
         <v>8063</v>
       </c>
-      <c r="H67" s="59">
+      <c r="H67" s="60">
         <v>9443</v>
       </c>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="58" t="s">
+      <c r="B68" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="C68" s="59">
+      <c r="C68" s="60">
         <v>125874</v>
       </c>
-      <c r="D68" s="59">
+      <c r="D68" s="60">
         <v>137196</v>
       </c>
-      <c r="E68" s="59">
+      <c r="E68" s="60">
         <v>11178</v>
       </c>
-      <c r="F68" s="59">
+      <c r="F68" s="60">
         <v>13288</v>
       </c>
-      <c r="G68" s="59">
+      <c r="G68" s="60">
         <v>10823</v>
       </c>
-      <c r="H68" s="59">
+      <c r="H68" s="60">
         <v>11011</v>
       </c>
     </row>
     <row r="69" spans="2:8">
-      <c r="B69" s="60" t="s">
+      <c r="B69" s="61" t="s">
         <v>210</v>
       </c>
-      <c r="C69" s="61">
+      <c r="C69" s="62">
         <v>240189</v>
       </c>
-      <c r="D69" s="61">
+      <c r="D69" s="62">
         <v>261243</v>
       </c>
-      <c r="E69" s="61">
+      <c r="E69" s="62">
         <v>101472</v>
       </c>
-      <c r="F69" s="61">
+      <c r="F69" s="62">
         <v>91961</v>
       </c>
-      <c r="G69" s="61">
+      <c r="G69" s="62">
         <v>65453</v>
       </c>
-      <c r="H69" s="61">
+      <c r="H69" s="62">
         <v>70835</v>
       </c>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="58" t="s">
+      <c r="B70" s="59" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="64" t="s">
+      <c r="B71" s="65" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="15.5">
-      <c r="B73" s="58" t="s">
+      <c r="B73" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="C73" s="63">
+      <c r="C73" s="64">
         <v>2018</v>
       </c>
-      <c r="D73" s="63">
+      <c r="D73" s="64">
         <v>2019</v>
       </c>
-      <c r="E73" s="63">
+      <c r="E73" s="64">
         <v>2020</v>
       </c>
-      <c r="F73" s="63">
+      <c r="F73" s="64">
         <v>2021</v>
       </c>
-      <c r="G73" s="63">
+      <c r="G73" s="64">
         <v>2022</v>
       </c>
-      <c r="H73" s="63">
+      <c r="H73" s="64">
         <v>2023</v>
       </c>
     </row>
@@ -20346,27 +20351,27 @@
       <c r="B74" t="s">
         <v>214</v>
       </c>
-      <c r="C74" s="55">
+      <c r="C74" s="56">
         <f>C62+C66</f>
         <v>220613</v>
       </c>
-      <c r="D74" s="55">
+      <c r="D74" s="56">
         <f t="shared" ref="D74:H74" si="0">D62+D66</f>
         <v>222200</v>
       </c>
-      <c r="E74" s="55">
+      <c r="E74" s="56">
         <f t="shared" si="0"/>
         <v>162850</v>
       </c>
-      <c r="F74" s="55">
+      <c r="F74" s="56">
         <f t="shared" si="0"/>
         <v>169895</v>
       </c>
-      <c r="G74" s="55">
+      <c r="G74" s="56">
         <f t="shared" si="0"/>
         <v>147916</v>
       </c>
-      <c r="H74" s="55">
+      <c r="H74" s="56">
         <f t="shared" si="0"/>
         <v>167805</v>
       </c>
@@ -20375,27 +20380,27 @@
       <c r="B75" t="s">
         <v>215</v>
       </c>
-      <c r="C75" s="55">
+      <c r="C75" s="56">
         <f>C63+C67</f>
         <v>40318</v>
       </c>
-      <c r="D75" s="55">
+      <c r="D75" s="56">
         <f t="shared" ref="D75:H75" si="1">D63+D67</f>
         <v>39797</v>
       </c>
-      <c r="E75" s="55">
+      <c r="E75" s="56">
         <f t="shared" si="1"/>
         <v>33068</v>
       </c>
-      <c r="F75" s="55">
+      <c r="F75" s="56">
         <f t="shared" si="1"/>
         <v>39018</v>
       </c>
-      <c r="G75" s="55">
+      <c r="G75" s="56">
         <f t="shared" si="1"/>
         <v>31718</v>
       </c>
-      <c r="H75" s="55">
+      <c r="H75" s="56">
         <f t="shared" si="1"/>
         <v>38481</v>
       </c>
@@ -20404,27 +20409,27 @@
       <c r="B76" t="s">
         <v>216</v>
       </c>
-      <c r="C76" s="55">
+      <c r="C76" s="56">
         <f>C75*$G$88</f>
         <v>36466.024042937868</v>
       </c>
-      <c r="D76" s="55">
+      <c r="D76" s="56">
         <f t="shared" ref="D76:H76" si="2">D75*$G$88</f>
         <v>35994.800308467646</v>
       </c>
-      <c r="E76" s="55">
+      <c r="E76" s="56">
         <f t="shared" si="2"/>
         <v>29908.688006643919</v>
       </c>
-      <c r="F76" s="55">
+      <c r="F76" s="56">
         <f t="shared" si="2"/>
         <v>35290.225857119643</v>
       </c>
-      <c r="G76" s="55">
+      <c r="G76" s="56">
         <f t="shared" si="2"/>
         <v>28687.666813678839</v>
       </c>
-      <c r="H76" s="55">
+      <c r="H76" s="56">
         <f t="shared" si="2"/>
         <v>34804.530760362424</v>
       </c>
@@ -20433,27 +20438,27 @@
       <c r="B77" t="s">
         <v>217</v>
       </c>
-      <c r="C77" s="55">
+      <c r="C77" s="56">
         <f>C75*$G$89</f>
         <v>1167.0417127691676</v>
       </c>
-      <c r="D77" s="55">
+      <c r="D77" s="56">
         <f t="shared" ref="D77:H77" si="3">D75*$G$89</f>
         <v>1151.9608870250152</v>
       </c>
-      <c r="E77" s="55">
+      <c r="E77" s="56">
         <f t="shared" si="3"/>
         <v>957.18377295130801</v>
       </c>
-      <c r="F77" s="55">
+      <c r="F77" s="56">
         <f t="shared" si="3"/>
         <v>1129.4120132156204</v>
       </c>
-      <c r="G77" s="55">
+      <c r="G77" s="56">
         <f t="shared" si="3"/>
         <v>918.10677726108588</v>
       </c>
-      <c r="H77" s="55">
+      <c r="H77" s="56">
         <f t="shared" si="3"/>
         <v>1113.868052707732</v>
       </c>
@@ -20462,27 +20467,27 @@
       <c r="B78" t="s">
         <v>218</v>
       </c>
-      <c r="C78" s="55">
+      <c r="C78" s="56">
         <f>C75*$G$90</f>
         <v>2685.0382309019583</v>
       </c>
-      <c r="D78" s="55">
+      <c r="D78" s="56">
         <f t="shared" ref="D78:H78" si="4">D75*$G$90</f>
         <v>2650.3414473735111</v>
       </c>
-      <c r="E78" s="55">
+      <c r="E78" s="56">
         <f t="shared" si="4"/>
         <v>2202.2135080972753</v>
       </c>
-      <c r="F78" s="55">
+      <c r="F78" s="56">
         <f t="shared" si="4"/>
         <v>2598.4627633645669</v>
       </c>
-      <c r="G78" s="55">
+      <c r="G78" s="56">
         <f t="shared" si="4"/>
         <v>2112.3082148853691</v>
       </c>
-      <c r="H78" s="55">
+      <c r="H78" s="56">
         <f t="shared" si="4"/>
         <v>2562.7004356202751</v>
       </c>
@@ -20493,10 +20498,10 @@
       </c>
     </row>
     <row r="83" spans="2:8">
-      <c r="B83" s="66" t="s">
+      <c r="B83" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="67" t="s">
+      <c r="C83" s="68" t="s">
         <v>221</v>
       </c>
       <c r="G83">
@@ -20507,10 +20512,10 @@
       </c>
     </row>
     <row r="84" spans="2:8">
-      <c r="B84" s="68" t="s">
+      <c r="B84" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="C84" s="69">
+      <c r="C84" s="70">
         <v>387723</v>
       </c>
       <c r="F84" t="s">
@@ -20520,15 +20525,15 @@
         <f>C85+C86</f>
         <v>350680</v>
       </c>
-      <c r="H84" s="54">
+      <c r="H84" s="55">
         <v>771496.00000000012</v>
       </c>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="70" t="s">
+      <c r="B85" s="71" t="s">
         <v>223</v>
       </c>
-      <c r="C85" s="71">
+      <c r="C85" s="72">
         <v>222953</v>
       </c>
       <c r="F85" t="s">
@@ -20538,15 +20543,15 @@
         <f>C87+C88</f>
         <v>11223</v>
       </c>
-      <c r="H85" s="54">
+      <c r="H85" s="55">
         <v>24690.600000000002</v>
       </c>
     </row>
     <row r="86" spans="2:8">
-      <c r="B86" s="68" t="s">
+      <c r="B86" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="C86" s="69">
+      <c r="C86" s="70">
         <v>127727</v>
       </c>
       <c r="F86" t="s">
@@ -20556,15 +20561,15 @@
         <f>C89+C90</f>
         <v>25821</v>
       </c>
-      <c r="H86" s="54">
+      <c r="H86" s="55">
         <v>56806.200000000004</v>
       </c>
     </row>
     <row r="87" spans="2:8">
-      <c r="B87" s="70" t="s">
+      <c r="B87" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="C87" s="71">
+      <c r="C87" s="72">
         <v>4421</v>
       </c>
       <c r="G87" t="s">
@@ -20572,57 +20577,57 @@
       </c>
     </row>
     <row r="88" spans="2:8">
-      <c r="B88" s="68" t="s">
+      <c r="B88" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="69">
+      <c r="C88" s="70">
         <v>6802</v>
       </c>
       <c r="F88" t="s">
         <v>216</v>
       </c>
-      <c r="G88" s="53">
+      <c r="G88" s="54">
         <f>G84/$C$84</f>
         <v>0.90446014293709687</v>
       </c>
     </row>
     <row r="89" spans="2:8">
-      <c r="B89" s="70" t="s">
+      <c r="B89" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="C89" s="71">
+      <c r="C89" s="72">
         <v>9100</v>
       </c>
       <c r="F89" t="s">
         <v>217</v>
       </c>
-      <c r="G89" s="53">
+      <c r="G89" s="54">
         <f t="shared" ref="G89:G90" si="5">G85/$C$84</f>
         <v>2.8945922733497883E-2</v>
       </c>
     </row>
     <row r="90" spans="2:8">
-      <c r="B90" s="72" t="s">
+      <c r="B90" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="C90" s="65">
+      <c r="C90" s="66">
         <v>16721</v>
       </c>
       <c r="F90" t="s">
         <v>218</v>
       </c>
-      <c r="G90" s="53">
+      <c r="G90" s="54">
         <f t="shared" si="5"/>
         <v>6.659651349030106E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
-      <c r="B91" s="56" t="s">
+      <c r="B91" s="57" t="s">
         <v>230</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="48" type="noConversion"/>
+  <phoneticPr fontId="49" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B71" r:id="rId1" location=":~:text=The%20number%20of%20new%20cars,2022%20(50%2C381%20versus%2046%2C567)." xr:uid="{D6FC7503-56E3-4D02-ABAF-AE1C4A4C08B4}"/>
   </hyperlinks>
